--- a/AAII_Financials/Quarterly/ARX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ARX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>ARX</t>
   </si>
@@ -656,198 +656,211 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>323700</v>
+      </c>
+      <c r="E8" s="3">
         <v>261100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>270300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>217800</v>
       </c>
-      <c r="G8" s="3">
-        <v>204700</v>
-      </c>
       <c r="H8" s="3">
+        <v>205900</v>
+      </c>
+      <c r="I8" s="3">
         <v>163500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>181200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>138600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>121400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>119800</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>106500</v>
+      </c>
+      <c r="E9" s="3">
         <v>115400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>78900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>73600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>69500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>62300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>75100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>62800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>59300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>51500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>217200</v>
+      </c>
+      <c r="E10" s="3">
         <v>145700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>191400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>144200</v>
       </c>
-      <c r="G10" s="3">
-        <v>135200</v>
-      </c>
       <c r="H10" s="3">
+        <v>136400</v>
+      </c>
+      <c r="I10" s="3">
         <v>101200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>106100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>75800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>62100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>68300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -863,49 +876,53 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
         <v>29400</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G12" s="3">
-        <v>-3000</v>
+      <c r="G12" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J12" s="3">
         <v>18700</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3">
         <v>2600</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,90 +962,99 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>36700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>56400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-1600</v>
-      </c>
       <c r="H14" s="3">
+        <v>-400</v>
+      </c>
+      <c r="I14" s="3">
         <v>-2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>5300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
         <v>-400</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E15" s="3">
         <v>10000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>5800</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>5500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>4900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1041,90 +1067,97 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E17" s="3">
         <v>266900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>249300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>217600</v>
       </c>
-      <c r="G17" s="3">
-        <v>175700</v>
-      </c>
       <c r="H17" s="3">
+        <v>180100</v>
+      </c>
+      <c r="I17" s="3">
         <v>156800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>169900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>143900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>132200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>114100</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>50500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-5800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>200</v>
       </c>
-      <c r="G18" s="3">
-        <v>29000</v>
-      </c>
       <c r="H18" s="3">
+        <v>25800</v>
+      </c>
+      <c r="I18" s="3">
         <v>6700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-5300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-10800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5700</v>
       </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1140,122 +1173,129 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="E20" s="3">
         <v>1900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>14200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>3100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>5400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E21" s="3">
         <v>2300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>24000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>12600</v>
       </c>
-      <c r="G21" s="3">
-        <v>23100</v>
-      </c>
       <c r="H21" s="3">
+        <v>19900</v>
+      </c>
+      <c r="I21" s="3">
         <v>11000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-4900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-4500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>11600</v>
       </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
       <c r="N21" s="3">
         <v>0</v>
       </c>
       <c r="O21" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E22" s="3">
         <v>2500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>-5200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1384700</v>
       </c>
-      <c r="G22" s="3">
-        <v>6900</v>
-      </c>
       <c r="H22" s="3">
+        <v>2500</v>
+      </c>
+      <c r="I22" s="3">
         <v>2600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>3000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>3100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>3000</v>
       </c>
       <c r="L22" s="3">
         <v>3000</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
+      <c r="M22" s="3">
+        <v>3000</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
@@ -1263,90 +1303,99 @@
       <c r="O22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>87400</v>
+      </c>
+      <c r="E23" s="3">
         <v>2000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-2200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1428400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>15500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>23000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-4300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>12000</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E24" s="3">
         <v>6100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-3100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-8100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>9900</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1386,90 +1435,99 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-4100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1437900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>7800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>20600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>9400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-9200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2100</v>
       </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-5200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1439700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>6500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>21000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>8100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-9000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>7100</v>
       </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1509,8 +1567,11 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1550,8 +1611,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1591,8 +1655,11 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1632,90 +1699,99 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-14200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-3100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-5400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-5200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1439700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>6500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>21000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>8100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-9000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>7100</v>
       </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1755,95 +1831,104 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-5200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1439700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>6500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>21000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>8100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-9000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>7100</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1859,8 +1944,9 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1876,35 +1962,36 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1572800</v>
+      </c>
+      <c r="E41" s="3">
         <v>1453600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1716200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1604000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1387700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1238000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1225700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1058300</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,35 +2004,38 @@
       <c r="O41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>85600</v>
+      </c>
+      <c r="E42" s="3">
         <v>201800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>41600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>69700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>46900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>64800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48600</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -1958,35 +2048,38 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>5988400</v>
+      </c>
+      <c r="E43" s="3">
         <v>5548300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>5142400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4838200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4739000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4166800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3737100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3478900</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1999,8 +2092,11 @@
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2040,35 +2136,38 @@
       <c r="O44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>80300</v>
+      </c>
+      <c r="E45" s="3">
         <v>85400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>88800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>101100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>101200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>202900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>101100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>159400</v>
       </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2081,35 +2180,38 @@
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>7831200</v>
+      </c>
+      <c r="E46" s="3">
         <v>7395600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7092900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6690800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6387500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5723600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5193100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4780200</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2122,35 +2224,38 @@
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>645400</v>
+      </c>
+      <c r="E47" s="3">
         <v>752100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>759600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>787400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>701400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>605000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>538100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>448000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2163,8 +2268,11 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2204,40 +2312,43 @@
       <c r="O48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E49" s="3">
         <v>214400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>215600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>212200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>213200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>201800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>147600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>50700</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
       </c>
       <c r="N49" s="3" t="s">
         <v>3</v>
@@ -2245,8 +2356,11 @@
       <c r="O49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2286,8 +2400,11 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2327,35 +2444,38 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E52" s="3">
         <v>78700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>65600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>61700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>87800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15100</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2368,8 +2488,11 @@
       <c r="O52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2409,35 +2532,38 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8943300</v>
+      </c>
+      <c r="E54" s="3">
         <v>8604100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>8263100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>7859400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>7496200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6715900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6094900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>5503600</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2450,8 +2576,11 @@
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2467,8 +2596,9 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2484,8 +2614,9 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2495,24 +2626,24 @@
       <c r="E57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F57" s="3">
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3">
         <v>17600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>10000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>17100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3">
         <v>8400</v>
       </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2525,8 +2656,11 @@
       <c r="O57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2534,31 +2668,31 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
       <c r="G58" s="3">
+        <v>0</v>
+      </c>
+      <c r="H58" s="3">
         <v>5000</v>
       </c>
-      <c r="H58" s="3">
-        <v>0</v>
-      </c>
       <c r="I58" s="3">
         <v>0</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>3100</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
@@ -2566,35 +2700,38 @@
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>497500</v>
+      </c>
+      <c r="E59" s="3">
         <v>472900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>438600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>10900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>506400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1230200</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2607,35 +2744,38 @@
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>691200</v>
+      </c>
+      <c r="E60" s="3">
         <v>657300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>661300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>204800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>210500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>637400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>169300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1515700</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2648,35 +2788,38 @@
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>120100</v>
+      </c>
+      <c r="E61" s="3">
         <v>120700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>118200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>121900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>121700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>121500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>121400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>118000</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
@@ -2689,35 +2832,38 @@
       <c r="O61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4985700</v>
+      </c>
+      <c r="E62" s="3">
         <v>4650900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4361700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>4435400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>4273800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3321600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>3381000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1705500</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2730,8 +2876,11 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2771,8 +2920,11 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2812,8 +2964,11 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2853,35 +3008,38 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>8199300</v>
+      </c>
+      <c r="E66" s="3">
         <v>7884200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7536700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7155600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7014000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6261500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5667900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5210200</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,8 +3052,11 @@
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2911,8 +3072,9 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2952,8 +3114,11 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2993,8 +3158,11 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3008,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>486200</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
         <v>486200</v>
@@ -3017,25 +3185,28 @@
         <v>486200</v>
       </c>
       <c r="J70" s="3">
+        <v>486200</v>
+      </c>
+      <c r="K70" s="3">
         <v>381800</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>381800</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3075,35 +3246,38 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1463400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1542100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1536900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1536300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-167500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-176300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-182800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-203800</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3116,8 +3290,11 @@
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3157,8 +3334,11 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3198,8 +3378,11 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3239,49 +3422,55 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>717400</v>
+      </c>
+      <c r="E76" s="3">
         <v>692600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>697700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>676100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-35600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-60300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-77500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-97700</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="3">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3">
         <v>-71300</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N76" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3321,95 +3510,104 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>78700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-5200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1439700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>6500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>21000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>8100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-9000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>7100</v>
       </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3425,35 +3623,36 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2300</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3466,8 +3665,11 @@
       <c r="O83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3507,8 +3709,11 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3548,8 +3753,11 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3589,8 +3797,11 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3630,8 +3841,11 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3671,49 +3885,55 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-68600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-21400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>61900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>73900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>217500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>91800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>241800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>276400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>123200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>144300</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3729,8 +3949,9 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3770,8 +3991,11 @@
       <c r="O91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3811,8 +4035,11 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3852,49 +4079,55 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>269700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-211600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>64700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-93100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-89700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-148900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-68200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-72700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-90300</v>
       </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3910,8 +4143,9 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3951,8 +4185,11 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P96" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3992,8 +4229,11 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4033,8 +4273,11 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4074,76 +4317,82 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-78300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>208600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>113700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1900</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="O100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>40200</v>
+      </c>
+      <c r="E101" s="3">
         <v>17900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-18600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>7900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>14800</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
@@ -4156,45 +4405,51 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>119800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-262800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>123400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>217400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>167800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>17700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>188000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>213900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>46200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>49500</v>
       </c>
-      <c r="M102" s="3">
-        <v>0</v>
-      </c>
       <c r="N102" s="3">
         <v>0</v>
       </c>
       <c r="O102" s="3">
+        <v>0</v>
+      </c>
+      <c r="P102" s="3">
         <v>0</v>
       </c>
     </row>
